--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.09299960452383</v>
+        <v>6.027612435735123</v>
       </c>
       <c r="D2" t="n">
-        <v>31.32572565242098</v>
+        <v>5.090430418518409</v>
       </c>
       <c r="E2" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F2" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.51936046493461</v>
+        <v>5.121896075551875</v>
       </c>
       <c r="D3" t="n">
-        <v>8.193585008930221</v>
+        <v>1.331457563951161</v>
       </c>
       <c r="E3" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F3" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.31213083016189</v>
+        <v>5.250721259901307</v>
       </c>
       <c r="D4" t="n">
-        <v>31.8800703398417</v>
+        <v>5.180511430224277</v>
       </c>
       <c r="E4" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F4" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.60129927356041</v>
+        <v>4.972711131953567</v>
       </c>
       <c r="D5" t="n">
-        <v>27.38829992316716</v>
+        <v>4.450598737514665</v>
       </c>
       <c r="E5" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.57204158687275</v>
+        <v>8.542956757866822</v>
       </c>
       <c r="D6" t="n">
-        <v>26.06125440620601</v>
+        <v>4.234953841008476</v>
       </c>
       <c r="E6" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F6" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.57878389451374</v>
+        <v>6.919052382858483</v>
       </c>
       <c r="D7" t="n">
-        <v>42.67849106581998</v>
+        <v>6.935254798195746</v>
       </c>
       <c r="E7" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F7" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.9740744395795</v>
+        <v>5.845787096431668</v>
       </c>
       <c r="D8" t="n">
-        <v>36.14203424382012</v>
+        <v>5.87308056462077</v>
       </c>
       <c r="E8" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F8" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.23960703202008</v>
+        <v>4.913936142703263</v>
       </c>
       <c r="D9" t="n">
-        <v>21.52732736152482</v>
+        <v>3.498190696247783</v>
       </c>
       <c r="E9" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F9" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.00596961109064</v>
+        <v>7.80097006180223</v>
       </c>
       <c r="D10" t="n">
-        <v>44.18985421005144</v>
+        <v>7.180851309133359</v>
       </c>
       <c r="E10" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F10" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.5374055756424</v>
+        <v>8.86232840604189</v>
       </c>
       <c r="D11" t="n">
-        <v>50.72772868491003</v>
+        <v>8.243255911297879</v>
       </c>
       <c r="E11" t="n">
-        <v>8.816672189180361</v>
+        <v>1.432709230741809</v>
       </c>
       <c r="F11" t="n">
-        <v>11.67875614598079</v>
+        <v>1.897797873721878</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
